--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/05_Anlage_1_Markenbestand.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/05_Anlage_1_Markenbestand.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anlage_unterschrieben" sheetId="1" r:id="R2b6b7ddd2595400d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datenraum_Fassung" sheetId="2" r:id="R0805db72dd634c1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fristen" sheetId="3" r:id="Rf2399e37216d45da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anlage_unterschrieben" sheetId="1" r:id="R981d060985884993"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datenraum_Fassung" sheetId="2" r:id="R0567c37b4bd04912"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fristen" sheetId="3" r:id="Rc7834458472943fe"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/05_Anlage_1_Markenbestand.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/05_Anlage_1_Markenbestand.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anlage_unterschrieben" sheetId="1" r:id="R981d060985884993"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datenraum_Fassung" sheetId="2" r:id="R0567c37b4bd04912"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fristen" sheetId="3" r:id="Rc7834458472943fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anlage_unterschrieben" sheetId="1" r:id="R057cfe254ce246a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datenraum_Fassung" sheetId="2" r:id="Re4717c88aa004a9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fristen" sheetId="3" r:id="R4fa36a83d6b24bf1"/>
   </x:sheets>
 </x:workbook>
 </file>
